--- a/bankole_sex_specific_splicing_2026/documentation/01_fiveSpecies/03_create_fiveSpecies_annotation_per_genome_14amm.xlsx
+++ b/bankole_sex_specific_splicing_2026/documentation/01_fiveSpecies/03_create_fiveSpecies_annotation_per_genome_14amm.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="232">
   <si>
     <t xml:space="preserve">Project Name</t>
   </si>
@@ -1757,6 +1757,20 @@
   </si>
   <si>
     <t xml:space="preserve">f"{proj}/submission/supplementary/fiveSpecies_{species}_full_annotation_w_component.csv"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add geneset to each annotation file
+Merged on geneID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add_geneset_2_full_annotation.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f"{proj}/submission/supplementary/fiveSpecies_{species}_full_annotation_w_component.csv"
+{PROJ}/submission/supplementary_files/fiveSpecies_annotations/link_files/nodes_with_geneset.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{PROJ}/submission/supplementary/fiveSpecies_{species}_full_annotation_w_genesetID.csv</t>
   </si>
   <si>
     <t xml:space="preserve">To cross species files with geneID (bove):
@@ -2512,7 +2526,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMJ116"/>
+  <dimension ref="A1:AMJ117"/>
   <sheetFormatPr defaultColWidth="7.9921875" defaultRowHeight="17.35" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -5764,62 +5778,76 @@
       <c r="A108" s="6"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="110" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="28"/>
-      <c r="D110" s="2" t="s">
+    <row r="109" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D109" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="E109" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="G109" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="H109" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D112" s="2" t="s">
+    <row r="111" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="28"/>
+      <c r="D111" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E111" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="G111" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="H112" s="2" t="s">
+      <c r="H111" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="114" s="39" customFormat="true" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="37"/>
-      <c r="B114" s="37"/>
-      <c r="C114" s="38"/>
-      <c r="D114" s="38" t="s">
+    <row r="113" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D113" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E114" s="38" t="s">
+      <c r="E113" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F114" s="38" t="s">
+      <c r="G113" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="G114" s="38" t="s">
+      <c r="H113" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="H114" s="38" t="s">
+    </row>
+    <row r="115" s="39" customFormat="true" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="37"/>
+      <c r="B115" s="37"/>
+      <c r="C115" s="38"/>
+      <c r="D115" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="I114" s="38"/>
-    </row>
-    <row r="116" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D116" s="2" t="s">
+      <c r="E115" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="G116" s="38" t="s">
-        <v>226</v>
+      <c r="F115" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="G115" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H115" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="I115" s="38"/>
+    </row>
+    <row r="117" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D117" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G117" s="38" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
